--- a/artfynd/A 19587-2024 artfynd.xlsx
+++ b/artfynd/A 19587-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119523289</v>
+        <v>119523294</v>
       </c>
       <c r="B2" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>789448</v>
+        <v>789410</v>
       </c>
       <c r="R2" t="n">
-        <v>7279379</v>
+        <v>7279262</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,13 +761,17 @@
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hack i tre granar</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119523309</v>
+        <v>119523289</v>
       </c>
       <c r="B3" t="n">
         <v>82305</v>
@@ -832,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789410</v>
+        <v>789448</v>
       </c>
       <c r="R3" t="n">
-        <v>7279113</v>
+        <v>7279379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119523348</v>
+        <v>119523299</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>90562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,31 +916,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789365</v>
+        <v>789439</v>
       </c>
       <c r="R4" t="n">
-        <v>7279118</v>
+        <v>7279145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,13 +991,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Hansi Gelter</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119523294</v>
+        <v>119523348</v>
       </c>
       <c r="B6" t="n">
-        <v>57326</v>
+        <v>57738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789410</v>
+        <v>789365</v>
       </c>
       <c r="R6" t="n">
-        <v>7279262</v>
+        <v>7279118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,11 +1206,6 @@
           <t>2024-08-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hack i tre granar</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1219,6 +1214,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Hansi Gelter</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119523299</v>
+        <v>119523309</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789439</v>
+        <v>789410</v>
       </c>
       <c r="R8" t="n">
-        <v>7279145</v>
+        <v>7279113</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
